--- a/data/trans_orig/P05A01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P05A01-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2007</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96037</t>
+          <t>93434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128345</t>
+          <t>127654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92091</t>
+          <t>92147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124731</t>
+          <t>125448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>197845</t>
+          <t>198464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>243396</t>
+          <t>244015</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116799</t>
+          <t>118136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149371</t>
+          <t>152543</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109881</t>
+          <t>110758</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144916</t>
+          <t>143800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235336</t>
+          <t>236197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>283493</t>
+          <t>283713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18448</t>
+          <t>18532</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38738</t>
+          <t>39259</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>15850</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36242</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39599</t>
+          <t>39707</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67672</t>
+          <t>67580</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>271008</t>
+          <t>266733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314213</t>
+          <t>312757</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262507</t>
+          <t>262857</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>306975</t>
+          <t>305866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>546343</t>
+          <t>546322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>606801</t>
+          <t>609915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141777</t>
+          <t>141823</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>184778</t>
+          <t>187978</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>148916</t>
+          <t>148849</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>192563</t>
+          <t>191319</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>302630</t>
+          <t>304609</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>362501</t>
+          <t>366145</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27094</t>
+          <t>26727</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51606</t>
+          <t>53076</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36375</t>
+          <t>35253</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63440</t>
+          <t>62875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69902</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106342</t>
+          <t>105517</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>121728</t>
+          <t>121160</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157918</t>
+          <t>157600</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83585</t>
+          <t>81680</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116920</t>
+          <t>115910</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>212187</t>
+          <t>213160</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>260795</t>
+          <t>261145</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124726</t>
+          <t>125725</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159070</t>
+          <t>160475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>140481</t>
+          <t>139811</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176647</t>
+          <t>177943</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>276852</t>
+          <t>276598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>324527</t>
+          <t>327761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>50,1%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27330</t>
+          <t>27391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50961</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64344</t>
+          <t>64208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94318</t>
+          <t>94125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98797</t>
+          <t>96637</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138347</t>
+          <t>136394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118127</t>
+          <t>115935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154495</t>
+          <t>153074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131676</t>
+          <t>133036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>167882</t>
+          <t>168466</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>260198</t>
+          <t>260007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>312069</t>
+          <t>312366</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152428</t>
+          <t>152533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190199</t>
+          <t>190487</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153178</t>
+          <t>152119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188314</t>
+          <t>188954</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>316667</t>
+          <t>315706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>370360</t>
+          <t>369042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,54%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39173</t>
+          <t>40009</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66785</t>
+          <t>66843</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38296</t>
+          <t>38232</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63374</t>
+          <t>63834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84285</t>
+          <t>85033</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>121527</t>
+          <t>122307</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132676</t>
+          <t>133497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>159108</t>
+          <t>159511</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133419</t>
+          <t>133079</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159966</t>
+          <t>159162</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>275132</t>
+          <t>273493</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>310909</t>
+          <t>312880</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42701</t>
+          <t>42304</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>68790</t>
+          <t>67840</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46892</t>
+          <t>47745</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72749</t>
+          <t>73713</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96884</t>
+          <t>95090</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>132485</t>
+          <t>134256</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>102028</t>
+          <t>102206</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>134067</t>
+          <t>133128</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>75074</t>
+          <t>76160</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>105765</t>
+          <t>108388</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>187491</t>
+          <t>184922</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>230424</t>
+          <t>229952</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,89%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>106967</t>
+          <t>107381</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>141146</t>
+          <t>139763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120050</t>
+          <t>120983</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>153856</t>
+          <t>152647</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>238241</t>
+          <t>237280</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282500</t>
+          <t>284547</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>20542</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>40116</t>
+          <t>40868</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40106</t>
+          <t>39612</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66417</t>
+          <t>67107</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>67056</t>
+          <t>66077</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99765</t>
+          <t>98672</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>285020</t>
+          <t>285486</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>338473</t>
+          <t>337850</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>295141</t>
+          <t>292304</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>348821</t>
+          <t>343033</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>591683</t>
+          <t>590834</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>663809</t>
+          <t>664857</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>181930</t>
+          <t>180872</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>227834</t>
+          <t>229221</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>162575</t>
+          <t>161198</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>210351</t>
+          <t>210412</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>357760</t>
+          <t>360114</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>420812</t>
+          <t>423209</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>81225</t>
+          <t>81543</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>119058</t>
+          <t>118511</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>114292</t>
+          <t>112689</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>155012</t>
+          <t>154145</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>206282</t>
+          <t>204561</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>259299</t>
+          <t>260175</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>449570</t>
+          <t>450679</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>501865</t>
+          <t>504822</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>469891</t>
+          <t>472175</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>525789</t>
+          <t>527752</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>935594</t>
+          <t>937476</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1014544</t>
+          <t>1012787</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,35%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>199754</t>
+          <t>198807</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>247920</t>
+          <t>253252</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>190849</t>
+          <t>187044</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>241700</t>
+          <t>239743</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>403072</t>
+          <t>403818</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>475881</t>
+          <t>477342</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>30345</t>
+          <t>30428</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>56387</t>
+          <t>55581</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>53515</t>
+          <t>53776</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>86592</t>
+          <t>86883</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>93701</t>
+          <t>92925</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>134170</t>
+          <t>132678</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1671918</t>
+          <t>1671606</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1787667</t>
+          <t>1788804</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1640577</t>
+          <t>1638876</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1756357</t>
+          <t>1753476</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3356520</t>
+          <t>3340558</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3518119</t>
+          <t>3503987</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1164232</t>
+          <t>1162947</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1277100</t>
+          <t>1272086</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1168636</t>
+          <t>1168849</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1280920</t>
+          <t>1275453</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2359015</t>
+          <t>2360398</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2512847</t>
+          <t>2519056</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>296613</t>
+          <t>293495</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>362488</t>
+          <t>362341</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>414955</t>
+          <t>420122</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>495318</t>
+          <t>495299</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>723227</t>
+          <t>734002</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>836954</t>
+          <t>836581</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2012</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>157344</t>
+          <t>158059</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>190350</t>
+          <t>191309</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>153082</t>
+          <t>154304</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>190548</t>
+          <t>187381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>322082</t>
+          <t>322448</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>371659</t>
+          <t>370368</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62302</t>
+          <t>61295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91050</t>
+          <t>89650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55519</t>
+          <t>55702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85610</t>
+          <t>85613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122420</t>
+          <t>125110</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>168645</t>
+          <t>168172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>29556</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53438</t>
+          <t>55559</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31128</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55424</t>
+          <t>55359</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65318</t>
+          <t>67068</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>103435</t>
+          <t>101667</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310659</t>
+          <t>312187</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>354698</t>
+          <t>357127</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322025</t>
+          <t>322461</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367099</t>
+          <t>368021</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>648174</t>
+          <t>649920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>712642</t>
+          <t>712534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111143</t>
+          <t>110581</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>151070</t>
+          <t>150300</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,82 +5657,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>21,87%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>29,73%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>126201</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>105810</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>146050</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>24,09%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>20,2%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>27,88%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>255979</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>226345</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>285065</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>24,87%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>21,99%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>29,88%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>126201</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>106333</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>145348</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>24,09%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>27,75%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>255979</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>229576</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>287420</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>24,87%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>22,3%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27617</t>
+          <t>28002</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56534</t>
+          <t>55613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,82 +5770,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>11,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>52898</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>39750</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>67399</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>10,1%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>12,87%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>93056</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>74000</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>115044</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>11,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>52898</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>39902</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>69213</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>93056</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>76276</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>115234</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>204987</t>
+          <t>204213</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>238570</t>
+          <t>237845</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>249837</t>
+          <t>248855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>280020</t>
+          <t>281240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>463755</t>
+          <t>464614</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>509509</t>
+          <t>509213</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,68%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70897</t>
+          <t>71400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102926</t>
+          <t>102540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49832</t>
+          <t>48938</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79727</t>
+          <t>78207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128886</t>
+          <t>128471</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171931</t>
+          <t>170986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24650</t>
+          <t>24884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21494</t>
+          <t>21604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>19476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39516</t>
+          <t>40325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>268081</t>
+          <t>268163</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>300751</t>
+          <t>301384</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>238643</t>
+          <t>240500</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>276140</t>
+          <t>277889</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>518632</t>
+          <t>519227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>570355</t>
+          <t>569445</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50774</t>
+          <t>50122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79856</t>
+          <t>79808</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75194</t>
+          <t>73304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108312</t>
+          <t>110451</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>131800</t>
+          <t>133330</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176616</t>
+          <t>175722</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35426</t>
+          <t>36432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25493</t>
+          <t>25851</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49696</t>
+          <t>50403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46813</t>
+          <t>45404</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>76663</t>
+          <t>76082</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129180</t>
+          <t>128967</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>157958</t>
+          <t>157884</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>122041</t>
+          <t>122987</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151212</t>
+          <t>151687</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>261669</t>
+          <t>260193</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>302531</t>
+          <t>301312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,71%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39057</t>
+          <t>39081</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64515</t>
+          <t>66317</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>55046</t>
+          <t>54976</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>83996</t>
+          <t>83404</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99941</t>
+          <t>102250</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>139322</t>
+          <t>140703</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26629</t>
+          <t>26045</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21962</t>
+          <t>22321</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>21377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42857</t>
+          <t>43634</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>173752</t>
+          <t>171865</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204941</t>
+          <t>203584</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>200327</t>
+          <t>200015</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>228618</t>
+          <t>227995</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>381780</t>
+          <t>382330</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>423643</t>
+          <t>425034</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58515</t>
+          <t>60061</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>89157</t>
+          <t>89651</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45664</t>
+          <t>46194</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72523</t>
+          <t>72205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113355</t>
+          <t>112102</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>153661</t>
+          <t>152858</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20040</t>
+          <t>20882</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>13909</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>29511</t>
+          <t>28259</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>406788</t>
+          <t>405335</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>455454</t>
+          <t>456091</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>462454</t>
+          <t>464501</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>512485</t>
+          <t>513844</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>882317</t>
+          <t>887040</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>957105</t>
+          <t>958346</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>165993</t>
+          <t>166778</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>214001</t>
+          <t>216464</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>144253</t>
+          <t>144569</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>190963</t>
+          <t>190811</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>323052</t>
+          <t>324457</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>390609</t>
+          <t>390750</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29515</t>
+          <t>29518</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55935</t>
+          <t>55648</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26567</t>
+          <t>26983</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52009</t>
+          <t>51886</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>61961</t>
+          <t>62297</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>97563</t>
+          <t>98493</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>528186</t>
+          <t>528792</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>582750</t>
+          <t>581100</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>587264</t>
+          <t>586957</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>638969</t>
+          <t>640145</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1133610</t>
+          <t>1133516</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1206717</t>
+          <t>1206251</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>169711</t>
+          <t>169313</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>221032</t>
+          <t>220533</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>152437</t>
+          <t>153038</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>201955</t>
+          <t>202128</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>337285</t>
+          <t>340161</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>408676</t>
+          <t>408603</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18228</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>40403</t>
+          <t>40879</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22459</t>
+          <t>22092</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>45666</t>
+          <t>44918</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>45193</t>
+          <t>45339</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>75639</t>
+          <t>78281</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2282682</t>
+          <t>2286459</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2396489</t>
+          <t>2394117</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2439274</t>
+          <t>2435719</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2549770</t>
+          <t>2551859</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4760047</t>
+          <t>4765199</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4918867</t>
+          <t>4919501</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>815909</t>
+          <t>813418</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>918403</t>
+          <t>917529</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>773161</t>
+          <t>767178</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>874913</t>
+          <t>872355</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1611615</t>
+          <t>1614482</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1756750</t>
+          <t>1749883</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>186662</t>
+          <t>188398</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>245324</t>
+          <t>248313</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>206727</t>
+          <t>209362</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>268851</t>
+          <t>271966</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>407652</t>
+          <t>411313</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>495291</t>
+          <t>501099</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2016</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155924</t>
+          <t>156506</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>191893</t>
+          <t>191149</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152485</t>
+          <t>151078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>186115</t>
+          <t>185631</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>319479</t>
+          <t>318329</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>368400</t>
+          <t>367508</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,32%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70773</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104962</t>
+          <t>103546</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55276</t>
+          <t>55052</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84288</t>
+          <t>85868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136133</t>
+          <t>135261</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>180170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22620</t>
+          <t>22689</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44650</t>
+          <t>44258</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36034</t>
+          <t>37340</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62504</t>
+          <t>63553</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64849</t>
+          <t>64641</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99191</t>
+          <t>101439</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310042</t>
+          <t>310222</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>353279</t>
+          <t>352298</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320597</t>
+          <t>322551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364719</t>
+          <t>367830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>645308</t>
+          <t>643715</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>706087</t>
+          <t>705667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>117784</t>
+          <t>120098</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>157334</t>
+          <t>161946</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127927</t>
+          <t>127525</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>170234</t>
+          <t>169687</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>256508</t>
+          <t>255030</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>315528</t>
+          <t>315904</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22255</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44904</t>
+          <t>45569</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20901</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44075</t>
+          <t>44160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47246</t>
+          <t>48385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81159</t>
+          <t>80543</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>248333</t>
+          <t>246474</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274466</t>
+          <t>273494</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>255596</t>
+          <t>255050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>283046</t>
+          <t>283388</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>511513</t>
+          <t>513566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>549490</t>
+          <t>550696</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39602</t>
+          <t>39317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64250</t>
+          <t>65367</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46074</t>
+          <t>48142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74012</t>
+          <t>76427</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92795</t>
+          <t>93882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130160</t>
+          <t>129857</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13099</t>
+          <t>13276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>238537</t>
+          <t>239069</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>275245</t>
+          <t>275454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>243585</t>
+          <t>245126</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>281808</t>
+          <t>282923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>496812</t>
+          <t>495401</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>547413</t>
+          <t>550274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60163</t>
+          <t>58117</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90889</t>
+          <t>91370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65758</t>
+          <t>65413</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99928</t>
+          <t>100020</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133572</t>
+          <t>132614</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>178447</t>
+          <t>179447</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26043</t>
+          <t>26806</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48760</t>
+          <t>50829</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30390</t>
+          <t>29704</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56730</t>
+          <t>54834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62802</t>
+          <t>61956</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95066</t>
+          <t>97315</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110521</t>
+          <t>110622</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>139766</t>
+          <t>138451</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>127419</t>
+          <t>127583</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156115</t>
+          <t>156660</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>247045</t>
+          <t>244437</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>289016</t>
+          <t>286862</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62646</t>
+          <t>62881</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>91505</t>
+          <t>91339</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48249</t>
+          <t>47903</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73387</t>
+          <t>74141</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>118289</t>
+          <t>119431</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>158810</t>
+          <t>159646</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23951</t>
+          <t>24517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36047</t>
+          <t>36077</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>208667</t>
+          <t>209125</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>231171</t>
+          <t>232259</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>215313</t>
+          <t>216372</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>240289</t>
+          <t>240680</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>430247</t>
+          <t>433167</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>465944</t>
+          <t>466530</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28291</t>
+          <t>27157</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50512</t>
+          <t>49144</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42053</t>
+          <t>40569</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53270</t>
+          <t>52511</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84355</t>
+          <t>83904</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22703</t>
+          <t>21387</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>27725</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>377779</t>
+          <t>379686</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>431056</t>
+          <t>433023</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>388566</t>
+          <t>387685</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>441931</t>
+          <t>441128</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>782304</t>
+          <t>781446</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>854997</t>
+          <t>855369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,52%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>189958</t>
+          <t>190200</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>239819</t>
+          <t>240157</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>202782</t>
+          <t>203198</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>254843</t>
+          <t>255117</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>409852</t>
+          <t>408748</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>478620</t>
+          <t>481190</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25379</t>
+          <t>24859</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49928</t>
+          <t>49055</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36418</t>
+          <t>35371</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>63522</t>
+          <t>62786</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>68065</t>
+          <t>67302</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>101801</t>
+          <t>103786</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>609637</t>
+          <t>606188</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>653835</t>
+          <t>650668</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>667834</t>
+          <t>669389</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>711152</t>
+          <t>712477</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1290724</t>
+          <t>1291601</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1351093</t>
+          <t>1351860</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>108007</t>
+          <t>110518</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>148602</t>
+          <t>151454</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>87531</t>
+          <t>86944</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>127926</t>
+          <t>128395</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>209335</t>
+          <t>208519</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>266721</t>
+          <t>265135</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28228</t>
+          <t>28864</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>17403</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>38672</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31536</t>
+          <t>31555</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>59363</t>
+          <t>59809</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2358398</t>
+          <t>2352354</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2463259</t>
+          <t>2465028</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2471081</t>
+          <t>2468133</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2579615</t>
+          <t>2574743</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4857914</t>
+          <t>4855485</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5011271</t>
+          <t>5017726</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>760183</t>
+          <t>760094</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>856771</t>
+          <t>867740</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>731642</t>
+          <t>727895</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>830463</t>
+          <t>831038</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1523261</t>
+          <t>1515835</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1665136</t>
+          <t>1664846</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>149034</t>
+          <t>146103</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>200082</t>
+          <t>198607</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>204263</t>
+          <t>204163</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>261565</t>
+          <t>265938</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>364726</t>
+          <t>365690</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>446020</t>
+          <t>446835</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2023</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>286535</t>
+          <t>285309</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>302960</t>
+          <t>302287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>256820</t>
+          <t>258846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>283653</t>
+          <t>283822</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>553150</t>
+          <t>553262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>582786</t>
+          <t>583205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>26134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32284</t>
+          <t>29834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17405</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46615</t>
+          <t>46990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -13979,97 +13979,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2786</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>659</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2741</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3168</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>2927</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>388576</t>
+          <t>384623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434762</t>
+          <t>433629</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>399007</t>
+          <t>398620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>431435</t>
+          <t>431358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>801554</t>
+          <t>799269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>855808</t>
+          <t>852503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,5%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73371</t>
+          <t>75869</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>117794</t>
+          <t>122136</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69310</t>
+          <t>69660</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>101267</t>
+          <t>100737</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>154989</t>
+          <t>157233</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>206729</t>
+          <t>209841</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>20421</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8959</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21984</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16582</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35050</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>256327</t>
+          <t>255441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>280943</t>
+          <t>279383</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>265625</t>
+          <t>263929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>291872</t>
+          <t>291552</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>527436</t>
+          <t>527791</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>564575</t>
+          <t>565810</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15790</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33301</t>
+          <t>32777</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34468</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57998</t>
+          <t>59423</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>55291</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87503</t>
+          <t>84389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13648</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33105</t>
+          <t>33609</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17466</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33922</t>
+          <t>34635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>36516</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60046</t>
+          <t>63446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>212508</t>
+          <t>212067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>247223</t>
+          <t>248839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>352690</t>
+          <t>346991</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>418564</t>
+          <t>415904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>575918</t>
+          <t>579052</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>654008</t>
+          <t>658384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,59%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55059</t>
+          <t>54553</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90005</t>
+          <t>90740</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42477</t>
+          <t>44109</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95673</t>
+          <t>98918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107080</t>
+          <t>102827</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>177492</t>
+          <t>171599</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31948</t>
+          <t>33085</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23117</t>
+          <t>22336</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44878</t>
+          <t>44744</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>142389</t>
+          <t>143027</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>158703</t>
+          <t>158595</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224635</t>
+          <t>223954</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245867</t>
+          <t>244903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372734</t>
+          <t>370793</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>402112</t>
+          <t>400797</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31217</t>
+          <t>30576</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33212</t>
+          <t>33544</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31457</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58381</t>
+          <t>59930</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>115</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>215658</t>
+          <t>217384</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>238794</t>
+          <t>239027</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>206246</t>
+          <t>206625</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>225168</t>
+          <t>224774</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>430129</t>
+          <t>430109</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>458612</t>
+          <t>458525</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>19610</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38638</t>
+          <t>37014</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19297</t>
+          <t>18999</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34684</t>
+          <t>34746</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42379</t>
+          <t>41843</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67714</t>
+          <t>66352</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>20524</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22378</t>
+          <t>22108</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>19921</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39498</t>
+          <t>37972</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>366683</t>
+          <t>369001</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>425660</t>
+          <t>427787</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>241055</t>
+          <t>209890</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>571002</t>
+          <t>570612</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>537738</t>
+          <t>511542</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>974047</t>
+          <t>971275</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>128549</t>
+          <t>127282</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>177263</t>
+          <t>178077</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>164277</t>
+          <t>161946</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>558846</t>
+          <t>594414</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>315694</t>
+          <t>313971</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>838291</t>
+          <t>846021</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,51%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54204</t>
+          <t>54972</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102126</t>
+          <t>106722</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>44232</t>
+          <t>39700</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>122576</t>
+          <t>122215</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>99758</t>
+          <t>106253</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>199571</t>
+          <t>204134</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>659319</t>
+          <t>656920</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>846547</t>
+          <t>841435</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>481469</t>
+          <t>481361</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>523416</t>
+          <t>522908</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1158538</t>
+          <t>1157566</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1383194</t>
+          <t>1392057</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>66116</t>
+          <t>70314</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>217222</t>
+          <t>219441</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>157763</t>
+          <t>157403</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>197372</t>
+          <t>196945</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>214957</t>
+          <t>211113</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>399925</t>
+          <t>401389</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>56075</t>
+          <t>57738</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>26825</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>48513</t>
+          <t>47999</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>45471</t>
+          <t>47892</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>96528</t>
+          <t>95659</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2648396</t>
+          <t>2644107</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2893326</t>
+          <t>2895736</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2225091</t>
+          <t>2236442</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2915021</t>
+          <t>2910916</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4915344</t>
+          <t>4847633</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5682650</t>
+          <t>5661836</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>438998</t>
+          <t>433685</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>621307</t>
+          <t>625530</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>587980</t>
+          <t>587837</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1326205</t>
+          <t>1312426</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1116765</t>
+          <t>1130477</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1950911</t>
+          <t>2068696</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>131385</t>
+          <t>134441</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>209956</t>
+          <t>211718</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>165751</t>
+          <t>163137</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>231197</t>
+          <t>230764</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>318560</t>
+          <t>314345</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>428628</t>
+          <t>423616</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
